--- a/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de horas que duerme</t>
+          <t>Menores según del número de horas que duerme (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 9,73</t>
+          <t>9,2; 9,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,75</t>
+          <t>9,26; 9,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,8</t>
+          <t>9,16; 9,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 9,45</t>
+          <t>8,76; 9,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,69</t>
+          <t>9,17; 9,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 9,71</t>
+          <t>9,19; 9,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,4</t>
+          <t>8,94; 9,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 9,1</t>
+          <t>8,67; 9,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,63</t>
+          <t>9,25; 9,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,65</t>
+          <t>9,26; 9,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,51</t>
+          <t>9,13; 9,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 9,18</t>
+          <t>8,77; 9,18</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,72</t>
+          <t>9,48; 9,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 9,92</t>
+          <t>9,62; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,22</t>
+          <t>9,05; 9,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,53</t>
+          <t>9,33; 9,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 9,18</t>
+          <t>8,97; 9,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 9,68</t>
+          <t>9,52; 9,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,92</t>
+          <t>9,72; 9,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,58</t>
+          <t>9,43; 9,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,17</t>
+          <t>9,03; 9,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9,62; 9,99</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9,84; 10,32</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9,48; 9,96</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9,04; 9,33</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,66; 10,08</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,64; 10,07</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,64; 10,09</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9,01; 9,28</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,97</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9,78; 10,12</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>9,62; 9,96</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,83; 10,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 9,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,66; 10,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,63; 10,06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 10,09</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,02; 9,3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,98</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,79; 10,11</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 9,95</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 9,25</t>
+          <t>9,06; 9,25</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,71</t>
+          <t>9,53; 9,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,91</t>
+          <t>9,68; 9,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 9,22</t>
+          <t>9,06; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,73</t>
+          <t>9,54; 9,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,92</t>
+          <t>9,7; 9,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,6</t>
+          <t>9,41; 9,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,16</t>
+          <t>8,99; 9,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,7</t>
+          <t>9,56; 9,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,62</t>
+          <t>9,49; 9,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,16</t>
+          <t>9,05; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 9,75</t>
+          <t>9,18; 9,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,76</t>
+          <t>9,24; 9,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,82</t>
+          <t>9,17; 9,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 9,47</t>
+          <t>8,75; 9,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,67</t>
+          <t>9,16; 9,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,71</t>
+          <t>9,19; 9,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,4</t>
+          <t>8,95; 9,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 9,11</t>
+          <t>8,66; 9,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,62</t>
+          <t>9,24; 9,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,64</t>
+          <t>9,29; 9,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 9,53</t>
+          <t>9,14; 9,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 9,18</t>
+          <t>8,77; 9,19</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,72</t>
+          <t>9,48; 9,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,9</t>
+          <t>9,63; 9,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,7</t>
+          <t>9,48; 9,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,22</t>
+          <t>9,06; 9,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 9,73</t>
+          <t>9,51; 9,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,54</t>
+          <t>9,32; 9,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,18</t>
+          <t>8,98; 9,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,93</t>
+          <t>9,72; 9,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,59</t>
+          <t>9,43; 9,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,17</t>
+          <t>9,04; 9,17</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,99</t>
+          <t>9,62; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 10,32</t>
+          <t>9,83; 10,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,96</t>
+          <t>9,51; 9,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,33</t>
+          <t>9,04; 9,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 10,08</t>
+          <t>9,67; 10,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,07</t>
+          <t>9,63; 10,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,09</t>
+          <t>9,65; 10,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,28</t>
+          <t>9,03; 9,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,97</t>
+          <t>9,69; 9,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 10,12</t>
+          <t>9,78; 10,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,25</t>
+          <t>9,08; 9,26</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 9,9</t>
+          <t>9,7; 9,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,21</t>
+          <t>9,07; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,93</t>
+          <t>9,71; 9,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,61</t>
+          <t>9,42; 9,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,15</t>
+          <t>9,0; 9,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,7</t>
+          <t>9,57; 9,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">

--- a/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,83</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,43</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,41</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,16</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,98</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,74</t>
+          <t>9,15; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,74</t>
+          <t>9,22; 9,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,82</t>
+          <t>8,93; 9,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 9,43</t>
+          <t>8,64; 9,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,7</t>
+          <t>9,2; 9,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,72</t>
+          <t>9,24; 9,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,39</t>
+          <t>9,17; 9,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 9,12</t>
+          <t>8,73; 9,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,61</t>
+          <t>9,24; 9,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,64</t>
+          <t>9,29; 9,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 9,51</t>
+          <t>9,11; 9,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 9,19</t>
+          <t>8,73; 9,09</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,42</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9,5</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9,5</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,74</t>
+          <t>9,5; 9,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 9,92</t>
+          <t>9,73; 10,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,7</t>
+          <t>9,33; 9,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,23</t>
+          <t>8,96; 9,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 9,73</t>
+          <t>9,46; 9,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,02</t>
+          <t>9,64; 9,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,54</t>
+          <t>9,49; 9,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 9,18</t>
+          <t>9,03; 9,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,69</t>
+          <t>9,51; 9,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,57</t>
+          <t>9,44; 9,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,17</t>
+          <t>9,02; 9,15</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,13</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,7</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,85</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,84</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,13</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9,66; 10,08</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9,63; 10,06</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9,64; 10,09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8,98; 9,26</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>9,62; 9,96</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,83; 10,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,96</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,32</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,67; 10,09</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 10,07</t>
+          <t>9,83; 10,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 10,1</t>
+          <t>9,47; 9,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,29</t>
+          <t>9,01; 9,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,96</t>
+          <t>9,69; 9,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 10,09</t>
+          <t>9,79; 10,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,96</t>
+          <t>9,62; 9,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 9,26</t>
+          <t>9,04; 9,22</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,79</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9,8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,72</t>
+          <t>9,54; 9,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,91</t>
+          <t>9,71; 9,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>9,42; 9,6</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8,99; 9,14</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,52; 9,71</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,91</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 9,74</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,93</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,16</t>
+          <t>9,05; 9,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,62</t>
+          <t>9,48; 9,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,03; 9,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,83</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,98</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9,45</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9,29</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,9</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.409556088552781</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.432622221288437</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.160521157562172</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>8.832144677163594</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>9.425334371139643</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>9.467569153851194</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>9.44273357568852</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>8.983195077750098</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.417632536938436</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>9.450700081620619</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>9.292231708873025</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>8.899490872058371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9,15; 9,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 9,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,93; 9,4</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,64; 9,06</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,2; 9,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,24; 9,75</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,17; 9,8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 9,31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9,24; 9,63</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9,29; 9,65</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9,11; 9,51</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 9,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>9.150245409409463</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>9.220758082379177</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8.92605822994587</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8.636277851949052</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>9.202933920596273</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>9.243100747768016</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9.166036232696273</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.726755804015811</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9.244053815437375</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>9.285723569444936</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>9.110392075634202</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.732231400165208</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.692088338234436</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.710383352988151</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.395916741932629</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.064257818043009</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.729563656270614</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9.746351407663184</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9.80499888036716</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>9.30953902057998</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9.629616031348384</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>9.648825317340149</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>9.514080251403515</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9.088283685460199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9,5</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,5; 9,73</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,73; 10,02</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,33; 9,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8,96; 9,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 9,92</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,49; 9,7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,68</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,92</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 9,58</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,02; 9,15</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>9.606629701792611</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>9.863097265823312</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.42392629427969</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.06042089213744</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>9.593926667972291</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>9.765122081811914</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9.585373581307326</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9.111239990516433</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9.600729493276829</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>9.816331807663973</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>9.50345445386842</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.084576942915792</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,05</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,7</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9.495670169322038</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>9.729940995056854</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>9.328078335102282</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>8.960219205208038</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>9.461859751865473</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>9.640746625472545</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>9.485456445043088</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>9.028076778587183</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9.508602370748683</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>9.723809684839853</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>9.435024028901639</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.018913663321298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9,66; 10,08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,63; 10,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 10,09</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8,98; 9,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 9,96</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,83; 10,33</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 9,94</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,01; 9,27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,98</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,79; 10,11</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 9,95</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,22</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.730934598311146</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.02038828941684</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.530365360041428</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.161390865870073</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>9.722267995566046</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>9.915587777907072</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>9.698962878860144</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.19230528896421</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>9.684832506598401</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>9.923785764044622</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9.584770696835838</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.153386424335576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>9.854841612848828</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.8367587755094</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.857220354168222</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.127233809676023</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.790331708419869</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>10.04732261243654</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>9.701562132240701</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.136258116561514</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.821075735335565</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>9.940520065519584</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>9.782971610361235</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.131455136872509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 9,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,99; 9,14</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,71</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,91</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,7</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9,05; 9,19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 9,7</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9,73; 9,88</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,62</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>9.6567416882259</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.629112816901099</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9.642871707280714</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8.984290528665484</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>9.615449321361007</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9.832970709082781</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>9.469142164842031</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.012628615223976</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>9.691620424284277</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>9.786477976766591</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>9.623382663899454</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.044367162472438</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.07506181501073</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.06100127116907</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.08961650675313</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.261495815261961</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.964734301204054</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.32805000334568</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9.943672943391128</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.268946810986346</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.981553461762648</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10.10659994024625</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>9.94779000267377</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.219843577119361</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>9.637394252746255</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>9.807737330826598</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.509073108734622</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.057991276864716</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>9.621690256596413</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>9.792403738930492</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>9.601496861439047</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>9.107802159569827</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9.629787924735822</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>9.800288771755454</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>9.554031594785314</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.081464186172594</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>9.540303151482465</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9.705894227607633</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>9.42374014686669</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8.988139821054755</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>9.524544694177933</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>9.691229195408974</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>9.513760991168251</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>9.046055605110039</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>9.571245584913976</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>9.726828747888032</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>9.484997006472435</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9.030551535696917</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.733373240927133</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.92261198601617</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.603750309980549</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.143586783943322</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>9.711627205958811</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>9.907885398717834</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>9.698176989022093</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.188894570506543</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>9.696596472510908</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>9.878616399224416</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>9.622101629564806</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.131871418130135</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
